--- a/content/W03/D1/briefs/C2_W03_D01_decisions_log_STUDENT.xlsx
+++ b/content/W03/D1/briefs/C2_W03_D01_decisions_log_STUDENT.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="58">
   <si>
     <t xml:space="preserve">How to use this log</t>
   </si>
@@ -177,6 +177,15 @@
   </si>
   <si>
     <t xml:space="preserve">The Q1 migration re-ran a batch, and every field on the pairs is identical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repeated, dates differ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep the later date, drop the earlier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One order recorded twice during the migration window; the later record matches the payment date</t>
   </si>
   <si>
     <t xml:space="preserve">status</t>
@@ -682,7 +691,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="100"/>
   </cols>
@@ -739,7 +748,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I64"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
@@ -1663,7 +1672,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
@@ -1930,7 +1939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
         <v>37</v>
       </c>
@@ -1955,8 +1964,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
@@ -2009,35 +2018,35 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>45</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>46</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>48</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>49</v>
       </c>
       <c r="C7" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>50</v>
@@ -2045,24 +2054,41 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C8" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>54</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/content/W03/D1/briefs/C2_W03_D01_decisions_log_STUDENT.xlsx
+++ b/content/W03/D1/briefs/C2_W03_D01_decisions_log_STUDENT.xlsx
@@ -1607,7 +1607,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>clinics</t>
+          <t>sites</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
@@ -1722,7 +1722,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>invoices</t>
+          <t>claims</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
@@ -1745,11 +1745,11 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>remittances</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>11289</v>
+        <v>11343</v>
       </c>
       <c r="C12" s="5">
         <f>SUMIFS(Log!$F$5:$F$64,Log!$C$5:$C$64,A12,Log!$H$5:$H$64,"removes rows")</f>

--- a/content/W03/D1/briefs/C2_W03_D01_decisions_log_STUDENT.xlsx
+++ b/content/W03/D1/briefs/C2_W03_D01_decisions_log_STUDENT.xlsx
@@ -529,7 +529,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>How to use this log</t>
+          <t>How do you fill this log?</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Decisions log</t>
+          <t>Which rows did the group change, remove or keep on purpose, and why?</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Input equals clean plus removed, file by file</t>
+          <t>Do rows in equal clean rows plus rows removed, file by file?</t>
         </is>
       </c>
     </row>
@@ -1868,14 +1868,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rows from the Week 1 Wednesday log, in Kalpa Retail</t>
+          <t>Which rows did the Week 1 Wednesday log hold for Kalpa Retail?</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>The shape you already know. Your rows are about Kalpa Health's files.</t>
+          <t>The shape you already know, in rupees. Your rows are about Kalpa Health's files, in dollars.</t>
         </is>
       </c>
     </row>

--- a/content/W03/D1/briefs/C2_W03_D01_decisions_log_STUDENT.xlsx
+++ b/content/W03/D1/briefs/C2_W03_D01_decisions_log_STUDENT.xlsx
@@ -55,7 +55,8 @@
     </font>
     <font>
       <name val="Arial"/>
-      <i val="1"/>
+      <b val="1"/>
+      <color rgb="001A0F5C"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -84,7 +85,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -106,11 +107,55 @@
         <color rgb="00B8B2D6"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B8B2D6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B8B2D6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B8B2D6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B8B2D6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B8B2D6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B8B2D6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B8B2D6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B8B2D6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -140,6 +185,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1855,7 +1902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1868,14 +1915,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Which rows did the Week 1 Wednesday log hold for Kalpa Retail?</t>
+          <t>What does one row of a decisions log hold, column by column?</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>The shape you already know, in rupees. Your rows are about Kalpa Health's files, in dollars.</t>
+          <t>One invented row in the Week 1 Wednesday shape, then what each column takes. Your rows are about Kalpa Health's files.</t>
         </is>
       </c>
     </row>
@@ -1909,111 +1956,118 @@
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>order_id</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Repeated</t>
+          <t>Empty</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Keep one row per order: the first copy, or the copy that validates where one copy's amount will not convert</t>
+          <t>Keep and flag</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>201 rows for 186 orders, and 14 of the 15 extra rows sit in Q1, the migration's quarter</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Will not convert, on one copy of a repeated order</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>Set aside with the duplicates; its twin, whose amount converts, stays</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>Keeping the first copy would keep the one that cannot be summed, and Q1 would sit Rs 1,790 short of the books</t>
+          <t>The visit happened and its outcome is unknown: dropping the row would remove a real booking, and a default would invent an outcome</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Empty</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Keep and flag</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>It happened and its fate is unknown: dropping it would remove a booked order from Q2, and a default would invent a delivery or a cancellation</t>
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>What each column takes</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>amount</t>
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Field</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Largest Q2 order, 1.66 times the next</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>Keep and flag, shown both ways</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>Large is not wrong: a Business-segment account with orders in both quarters, every field valid</t>
-        </is>
-      </c>
+          <t>The column the decision is about, as the file names it</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="13" t="n"/>
+      <c r="E8" s="14" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>What you saw, in a few words another group could check</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="14" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>How many rows the decision touches, counted from the file and never estimated</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="14" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>A reason that restates the issue is not a reason. The kept row is the one an auditor asks about, so it goes in the log too.</t>
-        </is>
-      </c>
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Keep, keep and flag, remove, or change, and how</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="14" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Why, in a sentence an auditor would accept; a reason that restates the issue is not a reason, and a kept row belongs in the log too</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="14" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B10:E10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>